--- a/Bigpy/Py_Scrap/data/you_crawl_result.xlsx
+++ b/Bigpy/Py_Scrap/data/you_crawl_result.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="111">
   <si>
     <t>작성자</t>
   </si>
@@ -26,6 +26,24 @@
   </si>
   <si>
     <t>프로필이미지</t>
+  </si>
+  <si>
+    <t>@뭐다안된대</t>
+  </si>
+  <si>
+    <t>2026에도 들으러 온 사람들 손</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>@김준희-w4g</t>
+  </si>
+  <si>
+    <t>2025년인데 이거 보는 사람 출석체크 하자</t>
+  </si>
+  <si>
+    <t>112</t>
   </si>
   <si>
     <t>@jihunyang1556</t>
@@ -73,25 +91,26 @@
 괴로움이 사무쳐서 노래를 부른다 그리움에 파묻혀서 그대를 부른다</t>
   </si>
   <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>@키에에엑</t>
+    <t>198</t>
+  </si>
+  <si>
+    <t>@252유리미</t>
+  </si>
+  <si>
+    <t>2026년에도 듣는사람 손? 
+지금들어도 노래 넘 좋음</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>@클라쓰1</t>
   </si>
   <si>
     <t>2:19 웅장한 멜로디 맛이 개지림</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>@wwgd1017</t>
-  </si>
-  <si>
-    <t>가사 진짜 대박 잘썻다....속사포랩하는 음유시인ㄷㄷ</t>
-  </si>
-  <si>
-    <t>31</t>
+    <t>16</t>
   </si>
   <si>
     <t>@수산나-y6n</t>
@@ -100,16 +119,25 @@
     <t>인간관계에 지쳐서 힘들때 들으면 한없이 눈물나는 노래... ㅠㅠ</t>
   </si>
   <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>@뭐다안된대</t>
-  </si>
-  <si>
-    <t>2026에도 들으러 온 사람들 손</t>
-  </si>
-  <si>
-    <t>38</t>
+    <t>183</t>
+  </si>
+  <si>
+    <t>@자유-f8u</t>
+  </si>
+  <si>
+    <t>아웃사이더 노래들을 때마다 생각하는거:이건 아웃사이더 밖에 못 부른다</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>@gwg0112</t>
+  </si>
+  <si>
+    <t>외롭고 힘들고 자살 생각만 했던 우울했던 시절에 이 노래 들으면서 버텼던 기억이 나네...</t>
+  </si>
+  <si>
+    <t>26</t>
   </si>
   <si>
     <t>@cksaldlfp123</t>
@@ -118,25 +146,16 @@
     <t>고등학교때 힘들었을 때 쉬는 시간에 엎드려서 이 노래 들으면서 위로받고 버텼는데 지금 들어도 가사가 너무 좋다</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>@김준희-w4g</t>
-  </si>
-  <si>
-    <t>2025년인데 이거 보는 사람 출석체크 하자</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>@gwg0112</t>
-  </si>
-  <si>
-    <t>외롭고 힘들고 자살 생각만 했던 우울했던 시절에 이 노래 들으면서 버텼던 기억이 나네...</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>25</t>
+  </si>
+  <si>
+    <t>@권보근-f4b</t>
+  </si>
+  <si>
+    <t>난 수시에도 정시에도 어디에도 속하지 못해</t>
+  </si>
+  <si>
+    <t>74</t>
   </si>
   <si>
     <t>@광부캐논진심</t>
@@ -145,7 +164,34 @@
     <t>진짜 가사도 너무 좋고 리듬도 좋고 슬프고 간절한 감정이 제대로 실려가지고 너무 좋다...</t>
   </si>
   <si>
-    <t>150</t>
+    <t>151</t>
+  </si>
+  <si>
+    <t>@약사-e2d</t>
+  </si>
+  <si>
+    <t>외톨이에서 주변인이돼고 주인공이돼는건가</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>@thanatomakia</t>
+  </si>
+  <si>
+    <t>보통 저렇게 빠르게 말하면 뭐라고 하는건지 못알아 듣겠고 박자감이 엉망이 되던데, 이 가수는 그걸 잡아내는구나..</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>@불주먹-u7n</t>
+  </si>
+  <si>
+    <t>개인적으로 외톨이보다 좋네 ㅋ</t>
+  </si>
+  <si>
+    <t>117</t>
   </si>
   <si>
     <t>@ParkSimBa</t>
@@ -154,252 +200,83 @@
     <t>왜 하자고 해 왜 하자고 해</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>@Scarycatnextdoor</t>
+  </si>
+  <si>
+    <t>와 이거 내 초딩때 최애곡인데ㅋㅋㅋㅋㅋㅠㅜㅠㅠ이거 켜놓고 그랜드체이스 뚝딱 조졌었는데 그립다</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>@mk9nzm6</t>
+  </si>
+  <si>
+    <t>omg the blend of classical instruments and Outsider's rap is perfect!</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>@RedFox-RFX</t>
+  </si>
+  <si>
+    <t>사람 사귀는게 제일 어려운거라는거 확연히 깨닫음</t>
+  </si>
+  <si>
+    <t>@gpa223</t>
+  </si>
+  <si>
+    <t>직장은 돈벌려고 가는건데 왜 인간관계때문에 이리 힘든지 ㅠㅠ</t>
+  </si>
+  <si>
+    <t>@duuuwo</t>
+  </si>
+  <si>
+    <t>16년 전 첫사랑을 만나러 갈때마다 MP3에 넣고 들었던 명곡...
+가끔 그때의 향기가 그립다...</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>@자유-f8u</t>
-  </si>
-  <si>
-    <t>아웃사이더 노래들을 때마다 생각하는거:이건 아웃사이더 밖에 못 부른다</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>@자몽-q8s</t>
-  </si>
-  <si>
-    <t>아 진짜 몇 백번을 들었는데, 갑자기 외톨이 알고리즘 떠서 여기까지 왔네ㅠㅜ</t>
-  </si>
-  <si>
-    <t>@Scarycatnextdoor</t>
-  </si>
-  <si>
-    <t>와 이거 내 초딩때 최애곡인데ㅋㅋㅋㅋㅋㅠㅜㅠㅠ이거 켜놓고 그랜드체이스 뚝딱 조졌었는데 그립다</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>@Icestar-v3l</t>
   </si>
   <si>
     <t>핵공감 가사가 나의 심금을 울리네..</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>@김동민-r3</t>
-  </si>
-  <si>
-    <t>삶에 대한 열정이나 희망 따위는 없어
-흘러가는대로 그냥 숨쉬고 있을뿐
-무미건조하게 매일 반복 되는 일상이란
-깨어 있지만 꿈 속을 헤엄치는 기분
-세상과 나의 끊임없이 계속되는 불협화음
-굳게 닫힌 마음의 문에 자물쇠를 걸었다
-(긴 긴) 외로움으로 녹이슨 키를 꺼내들어 (키를 꺼내들어)
-풀리지 않는 괴리감으로 나를 묶은 족쇄가
-내 목을 조여와 (내 목을 조여와)
-울리지않는 전화기를 들었다 놨다
-밤새도록 너를 기다려 (너를 기다려)
-나는 관심이 필요해 나는 대화가 필요해
-너의 손길이 필요해 작은 사랑이 필요해
-점점 꺼져가는 도화선에 불을 지펴줘 (불을 지펴줘)
-난 여기에도 저기에도 어디에도 섞이지 못해
-너에게도 그녀에게도 누구에게도 속하지 못해
-주위를 서성거리며 너의 곁을 맴돌아 (곁을 맴돌아)
-난 여기에도 저기에도 어디에도 섞이지 못해
-너에게도 그녀에게도 누구에게도 속하지 못해
-주위를 서성거리며 너의 곁을 맴돌아 (곁을 맴돌아)
-달빛은 알아줄까 외로운 이 밤을
-별빛은 알아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다
-그리움에 파묻혀서 그대를 부른다
-달빛은 알아줄까 외로운 이 밤을
-별빛은 알아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다
-그리움에 파묻혀서 그대를 부른다
-주위를 서성거리며 너의 곁을 맴돌아
-변화가 두려워 섞이지 못하고 주위를 겉돌아
-인연의 사슬을 풀어 줄 사람을 찾아 노래를 부르네
-바람따라 구름따라 세상을 떠돌아
-넌 어디로 갔을까 날 버리고 머머머머머 멀어진
-너마저 저저저저저 저 멀리 아무도 모르는곳으로
-떠나가고파 사랑에 굶주린 나는 언제나 배고파
-손가락질 조차 그리워
-관심조차 과분해서 사랑조차 사치스러워
-언제부턴가 내 곁에 붙어 다니는 그림자가
-달을 가릴때 내 마음은 너를 그린다
-난 끊임없이 주문을 외운다
-내게는 너 없는 하루하루가 너무나 두려워
-보고 싶어 만지고 싶어 느끼고 싶어도
-말없이 마냥 습관처럼 손톱을 깨물어
-난 여기에도 저기에도 어디에도 섞이지 못해
-너에게도 그녀에게도 누구에게도 속하지 못해
-주위를 서성거리며 너의 곁을 맴돌아 (곁을 맴돌아)
-난 여기에도 저기에도 어디에도 섞이지 못해
-너에게도 그녀에게도 누구에게도 속하지 못해
-주위를 서성거리며 너의 곁을 맴돌아 (곁을 맴돌아)
-달빛은 알아줄까 외로운 이 밤을
-별빛은 알아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다
-그리움에 파묻혀서 그대를 부른다
-달빛은 알아줄까 외로운 이 밤을
-별빛은 알아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다
-그리움에 파묻혀서 그대를 부른다
-난 여기에도 저기에도 어디에도 섞이지 못해
-너에게도 그녀에게도 누구에게도 속하지 못해
-주위를 서성거리며 너의 곁을 맴돌아
-난 여기에도 저기에도 어디에도 섞이지 못해
-너에게도 그녀에게도 누구에게도 속하지 못해
-주위를 서성거리며 너의 곁을 맴돌아
-달빛은 알아줄까 외로운 이 밤을
-별빛은 알아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다
-그리움에 파묻혀서 그대를 부른다
-달빛은 알아줄까 외로운 이 밤을
-별빛은 알아줄까 상처받은 맘을
-괴로움이 사무쳐서 노래를 부른다
-그리움에 파묻혀서 그대를 부른다</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>@gpa223</t>
-  </si>
-  <si>
-    <t>직장은 돈벌려고 가는건데 왜 인간관계때문에 이리 힘든지 ㅠㅠ</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>@MrAls6538</t>
-  </si>
-  <si>
-    <t>이 시절에 mp3에 다운 받아서 아웃사이더 전곡 산책하면서 들었는데 그 때 그 감성이 잊히지 않는다. 그 때로 돌아가고 싶다</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>@buddy3832</t>
-  </si>
-  <si>
-    <t>아웃사이더 최고의 명곡</t>
-  </si>
-  <si>
-    <t>@Eren-6666</t>
-  </si>
-  <si>
-    <t>2019년에 들어도 좋네 노래가... 한때 차트 휩쓸었던덴 다 이유가 있다</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>@psu01016</t>
-  </si>
-  <si>
-    <t>외톨이도 좋지만 이 곡이 최고다...</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>@TV-or2zd</t>
-  </si>
-  <si>
-    <t>반주 음 존나좋네</t>
-  </si>
-  <si>
-    <t>@흉부외과전문오랑</t>
-  </si>
-  <si>
-    <t>어렸을 때 그렇게 좋아했었는데 왜 그렇게 좋아했나 싶을 때마다 한 번씩 들으면 아 좋아할만했다 싶은 래퍼 랩 잘하는 사람이야 그때나 지금이나 많았지만 아웃사이더 특유의 감성은 아직도 독보적이라고 느껴지네</t>
-  </si>
-  <si>
-    <t>@loadbang1</t>
-  </si>
-  <si>
-    <t>전 어디에 속해야 하는걸까요...여기를가도 저기를 가도 섞이지 못하고 겉도네요.잘하고 싶은데 안되는 심정을 다들 무시하니 저도 아웃사이더 마인드가 생기더군요.그냥...뭐랄까...굳이 섞이려는 시도를 하는 에너지가 아까워서 그냥 지켜봐요.어차피 인생은 혼자. 그럴 팔자라면...겉도는대로 살아갈려구요.</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>@TV-qt2zr</t>
-  </si>
-  <si>
-    <t>아웃사이더는 랩을 너무잘함ㅇㅈ.</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>@김동욱-k6s</t>
-  </si>
-  <si>
-    <t>진짜 아웃사이더노래는 소름끼치도록 노래가 좋아...ㅎㄷㄷ 먼가가</t>
-  </si>
-  <si>
-    <t>@RedFox-RFX</t>
-  </si>
-  <si>
-    <t>사람 사귀는게 제일 어려운거라는거 확연히 깨닫음</t>
-  </si>
-  <si>
-    <t>@민수심-p7f</t>
-  </si>
-  <si>
-    <t>노래가 슬프다....
-그러면서 좋다.</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>@풍선껌a</t>
-  </si>
-  <si>
-    <t>힝힝ㅠ가사엄더</t>
-  </si>
-  <si>
-    <t>@돼지국밥전도사</t>
-  </si>
-  <si>
-    <t>진짜 존나게 좋은데 존나게 슬프고 존나게 우울하게 만드는 노래다</t>
+    <t>@followthedmntrainCJ</t>
+  </si>
+  <si>
+    <t>i have no idea what is going on lol</t>
+  </si>
+  <si>
+    <t>@Mapache_emperor</t>
+  </si>
+  <si>
+    <t>Me encanta la cancion, realmente la disfrute y es un tema importante entre mi esposa y yo</t>
+  </si>
+  <si>
+    <t>@그리.피스</t>
+  </si>
+  <si>
+    <t>예전 힙합은 랩에 영어보다 한글이 많아서 좋았는데 요즘은 이해도 못하는 영어만 쓰고...부르는 사람이나 듣는 사람 둘다 무슨 뜻인지 모르고 좋아함</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>@홍서진-g3l</t>
+  </si>
+  <si>
+    <t>뮤비를 찍으라고 했는데 영화를 찍었네</t>
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>@bluegm2713</t>
-  </si>
-  <si>
-    <t>따라부르기 진짜.. 아웃사이더는 전설이다</t>
-  </si>
-  <si>
-    <t>@mk9nzm6</t>
-  </si>
-  <si>
-    <t>omg the blend of classical instruments and Outsider's rap is perfect!</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>@benatakr</t>
-  </si>
-  <si>
-    <t>아웃사이더 완전 좋음ㅎㅎㅎㅎ</t>
   </si>
   <si>
     <t>@ab-qy1xm</t>
@@ -409,55 +286,109 @@
 근데 너무 깔끔하게사라져서 곡 듣고나면 '어? 내가 뭘 들었었지??'라는 생각이 들음 ㅋㅋㅋㅋㅋ</t>
   </si>
   <si>
+    <t>@김동욱-k6s</t>
+  </si>
+  <si>
+    <t>진짜 아웃사이더노래는 소름끼치도록 노래가 좋아...ㅎㄷㄷ 먼가가</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>@tyan6175</t>
+  </si>
+  <si>
+    <t>갑자기 생각나서 왔는데 뭔가 마음이 복잡해지네...</t>
+  </si>
+  <si>
+    <t>@Eren-6666</t>
+  </si>
+  <si>
+    <t>2019년에 들어도 좋네 노래가... 한때 차트 휩쓸었던덴 다 이유가 있다</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>@buddy3832</t>
+  </si>
+  <si>
+    <t>아웃사이더 최고의 명곡</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>@bluegm2713</t>
+  </si>
+  <si>
+    <t>따라부르기 진짜.. 아웃사이더는 전설이다</t>
+  </si>
+  <si>
+    <t>@TV-or2zd</t>
+  </si>
+  <si>
+    <t>반주 음 존나좋네</t>
+  </si>
+  <si>
+    <t>@이준영-h3x6h</t>
+  </si>
+  <si>
+    <t>이제야 이 노래의 가사를 이해했다</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>@MrAls6538</t>
+  </si>
+  <si>
+    <t>이 시절에 mp3에 다운 받아서 아웃사이더 전곡 산책하면서 들었는데 그 때 그 감성이 잊히지 않는다. 그 때로 돌아가고 싶다</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>@돼지국밥전도사</t>
+  </si>
+  <si>
+    <t>진짜 존나게 좋은데 존나게 슬프고 존나게 우울하게 만드는 노래다</t>
+  </si>
+  <si>
+    <t>@_ju3424</t>
+  </si>
+  <si>
+    <t>아웃사이더 노래중에 제일 좋아하는 곡</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>@자몽-q8s</t>
+  </si>
+  <si>
+    <t>아 진짜 몇 백번을 들었는데, 갑자기 외톨이 알고리즘 떠서 여기까지 왔네ㅠㅜ</t>
+  </si>
+  <si>
+    <t>@hsko7887</t>
+  </si>
+  <si>
+    <t>왜 요즘은 이런 노래불러주는 가수가 없울까요</t>
+  </si>
+  <si>
     <t>@JGJ-zx6rz</t>
   </si>
   <si>
     <t>외톨이 주변인 2연타는 진짜 ㅠㅠ</t>
   </si>
   <si>
-    <t>@권보근-f4b</t>
-  </si>
-  <si>
-    <t>난 수시에도 정시에도 어디에도 속하지 못해</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>@wjddbsgh</t>
-  </si>
-  <si>
-    <t>뮤비를 이해한다면 당신은 천재입니다!</t>
-  </si>
-  <si>
-    <t>@드라마모노</t>
-  </si>
-  <si>
-    <t>이런 류의노래가 많이 나왔으면좋겠다</t>
-  </si>
-  <si>
-    <t>@ookkkok6962</t>
-  </si>
-  <si>
-    <t>아 가사 진짜 공감...ㅠㅠㅠ</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>@약사-e2d</t>
-  </si>
-  <si>
-    <t>외톨이에서 주변인이돼고 주인공이돼는건가</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>@hsko7887</t>
-  </si>
-  <si>
-    <t>왜 요즘은 이런 노래불러주는 가수가 없울까요</t>
+    <t>@흉부외과전문오랑</t>
+  </si>
+  <si>
+    <t>어렸을 때 그렇게 좋아했었는데 왜 그렇게 좋아했나 싶을 때마다 한 번씩 들으면 아 좋아할만했다 싶은 래퍼 랩 잘하는 사람이야 그때나 지금이나 많았지만 아웃사이더 특유의 감성은 아직도 독보적이라고 느껴지네</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -521,7 +452,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="@jihunyang1556"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="@뭐다안된대"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -559,7 +490,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="@키에에엑"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="@김준희-w4g"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -597,7 +528,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="@wwgd1017"/>
+        <xdr:cNvPr id="4" name="Picture 3" descr="@jihunyang1556"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -635,7 +566,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="@수산나-y6n"/>
+        <xdr:cNvPr id="5" name="Picture 4" descr="@252유리미"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -673,7 +604,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="@뭐다안된대"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="@클라쓰1"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -711,7 +642,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="@cksaldlfp123"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="@수산나-y6n"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -749,7 +680,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="@김준희-w4g"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="@자유-f8u"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -825,7 +756,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="@광부캐논진심"/>
+        <xdr:cNvPr id="10" name="Picture 9" descr="@cksaldlfp123"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -852,7 +783,159 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10" descr="@권보근-f4b"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="1905000"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11" descr="@광부캐논진심"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="2095500"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12" descr="@thanatomakia"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="2476500"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13" descr="@불주먹-u7n"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="2667000"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
@@ -863,13 +946,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="@김동민-r3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <xdr:cNvPr id="15" name="Picture 14" descr="@ParkSimBa"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -901,13 +984,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11" descr="@gpa223"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <xdr:cNvPr id="16" name="Picture 15" descr="@Scarycatnextdoor"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -939,13 +1022,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12" descr="@MrAls6538"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <xdr:cNvPr id="17" name="Picture 16" descr="@mk9nzm6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -977,13 +1060,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 13" descr="@buddy3832"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <xdr:cNvPr id="18" name="Picture 17" descr="@RedFox-RFX"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1015,13 +1098,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 14" descr="@Eren-6666"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <xdr:cNvPr id="19" name="Picture 18" descr="@gpa223"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1053,13 +1136,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 15" descr="@psu01016"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <xdr:cNvPr id="20" name="Picture 19" descr="@duuuwo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1091,13 +1174,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 16" descr="@TV-or2zd"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <xdr:cNvPr id="21" name="Picture 20" descr="@Icestar-v3l"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1129,13 +1212,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 17" descr="@흉부외과전문오랑"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <xdr:cNvPr id="22" name="Picture 21" descr="@followthedmntrainCJ"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1167,13 +1250,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 18" descr="@loadbang1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <xdr:cNvPr id="23" name="Picture 22" descr="@Mapache_emperor"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1205,13 +1288,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Picture 19" descr="@TV-qt2zr"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <xdr:cNvPr id="24" name="Picture 23" descr="@그리.피스"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1243,13 +1326,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Picture 20" descr="@김동욱-k6s"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <xdr:cNvPr id="25" name="Picture 24" descr="@홍서진-g3l"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1281,13 +1364,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Picture 21" descr="@RedFox-RFX"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <xdr:cNvPr id="26" name="Picture 25" descr="@ab-qy1xm"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1319,13 +1402,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Picture 22" descr="@민수심-p7f"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <xdr:cNvPr id="27" name="Picture 26" descr="@김동욱-k6s"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1333,6 +1416,44 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1828800" y="5143500"/>
+          <a:ext cx="419100" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Picture 27" descr="@tyan6175"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="5334000"/>
           <a:ext cx="419100" cy="419100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1756,36 +1877,27 @@
       <c r="C11" t="s">
         <v>33</v>
       </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
         <v>35</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
         <v>38</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>39</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1798,9 +1910,6 @@
       <c r="C14" t="s">
         <v>42</v>
       </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
@@ -1812,9 +1921,6 @@
       <c r="C15" t="s">
         <v>45</v>
       </c>
-      <c r="D15" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
@@ -1827,7 +1933,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1838,7 +1944,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -1849,7 +1955,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -1857,10 +1963,10 @@
         <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -1868,137 +1974,131 @@
         <v>58</v>
       </c>
       <c r="C20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>60</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>61</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>64</v>
       </c>
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>65</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>66</v>
       </c>
-      <c r="C23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>67</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>68</v>
       </c>
-      <c r="C24" t="s">
+      <c r="B25" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
+      <c r="C25" t="s">
         <v>70</v>
       </c>
-      <c r="B25" t="s">
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>71</v>
       </c>
-      <c r="C25" t="s">
+      <c r="B26" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
+      <c r="C26" t="s">
         <v>73</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>74</v>
       </c>
-      <c r="C26" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>75</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>76</v>
       </c>
-      <c r="C27" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>77</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>78</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>80</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>81</v>
       </c>
-      <c r="D29" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>82</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>83</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>84</v>
       </c>
-      <c r="D30" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>85</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>86</v>
       </c>
-      <c r="C31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -2006,41 +2106,32 @@
         <v>88</v>
       </c>
       <c r="C32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>89</v>
       </c>
-      <c r="D32" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>90</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>91</v>
       </c>
-      <c r="C33" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>92</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>93</v>
       </c>
-      <c r="C34" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>94</v>
       </c>
@@ -2048,27 +2139,21 @@
         <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>99</v>
       </c>
@@ -2076,41 +2161,32 @@
         <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
-      </c>
-      <c r="D37" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
-      </c>
-      <c r="D38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
-      </c>
-      <c r="D39" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>106</v>
       </c>
@@ -2118,24 +2194,18 @@
         <v>107</v>
       </c>
       <c r="C40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
         <v>108</v>
       </c>
-      <c r="D40" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>109</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>110</v>
-      </c>
-      <c r="C41" t="s">
-        <v>33</v>
-      </c>
-      <c r="D41" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
